--- a/Lab MB1 B/LISTADO COMPLETO MACROS/PUNTEOS FINALES.xlsx
+++ b/Lab MB1 B/LISTADO COMPLETO MACROS/PUNTEOS FINALES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Lab MB1 B\LISTADO COMPLETO MACROS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3099883-2201-42E2-AA83-7E40F1CB7D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7D8185-6717-443E-A15A-787AB624CF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F4BDE4DC-E94C-4D9E-A851-8F281B73FE4C}"/>
   </bookViews>
